--- a/data/durf-roadmap.xlsx
+++ b/data/durf-roadmap.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="218">
   <si>
     <t xml:space="preserve">DURF roadmap — how to edit this workbook</t>
   </si>
@@ -412,10 +412,34 @@
     <t xml:space="preserve">1 Digital sovereignty health CRIS/Repo Dashboard: chart with ratio of metadata records containing a link to a file (PDF) on the institutional domain, per repo over time.</t>
   </si>
   <si>
-    <t xml:space="preserve">2, 4, 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. aanvullen van datapunten UKBsis formate,OA. Pascal schrijf dit verder uit. Welke tussenstapjes.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Write a proposal (2)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Approval of the proposal (3)
+Collect data for the monitor (4)
+Develop the monitor (4 – 5)
+Launch of the monitor (6)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- data delivery (all insitutions)
+- development of the monitor (WUR?)</t>
   </si>
   <si>
     <t xml:space="preserve">Create inventory of existing tools and methods for full-text capture</t>
@@ -693,7 +717,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;€ &quot;#,##0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -745,6 +769,11 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i val="true"/>
@@ -854,7 +883,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -919,11 +948,15 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1641,7 +1674,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="38"/>
@@ -2103,7 +2136,7 @@
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
     </row>
-    <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15">
         <v>3</v>
       </c>
@@ -2122,19 +2155,19 @@
       <c r="F16" s="15">
         <v>6</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="16" t="s">
         <v>126</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>113</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="J16" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="K16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8" t="s">
+        <v>128</v>
+      </c>
       <c r="L16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2142,10 +2175,10 @@
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>78</v>
@@ -2170,13 +2203,13 @@
         <v>3</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E18" s="15">
         <v>12</v>
@@ -2198,13 +2231,13 @@
         <v>3</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E19" s="15">
         <v>24</v>
@@ -2226,13 +2259,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E20" s="15">
         <v>3</v>
@@ -2254,13 +2287,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E21" s="15">
         <v>12</v>
@@ -2282,10 +2315,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>120</v>
@@ -2312,13 +2345,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E23" s="15">
         <v>12</v>
@@ -2340,10 +2373,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>78</v>
@@ -2356,7 +2389,7 @@
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>80</v>
@@ -2370,13 +2403,13 @@
         <v>5</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E25" s="15">
         <v>6</v>
@@ -2398,10 +2431,10 @@
         <v>5</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>120</v>
@@ -2414,7 +2447,7 @@
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>80</v>
@@ -2428,10 +2461,10 @@
         <v>6</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>83</v>
@@ -2443,14 +2476,14 @@
         <v>25</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
@@ -2460,10 +2493,10 @@
         <v>6</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>78</v>
@@ -2475,14 +2508,14 @@
         <v>42</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
@@ -2492,10 +2525,10 @@
         <v>6</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>78</v>
@@ -2507,14 +2540,14 @@
         <v>45</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
@@ -2524,10 +2557,10 @@
         <v>6</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>120</v>
@@ -2546,7 +2579,7 @@
         <v>80</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
@@ -2556,10 +2589,10 @@
         <v>6</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>109</v>
@@ -2571,7 +2604,7 @@
         <v>9</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H31" s="8"/>
       <c r="I31" s="7" t="s">
@@ -2628,16 +2661,16 @@
         <v>24</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2645,16 +2678,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="D2" s="16">
+        <v>178</v>
+      </c>
+      <c r="D2" s="17">
         <v>92000</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2662,16 +2695,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="D3" s="16">
+        <v>181</v>
+      </c>
+      <c r="D3" s="17">
         <v>3000</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2679,16 +2712,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="17">
+        <v>20000</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>182</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D4" s="16">
-        <v>20000</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2696,16 +2729,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D5" s="16">
+        <v>186</v>
+      </c>
+      <c r="D5" s="17">
         <v>40000</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2713,16 +2746,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="D6" s="16">
+        <v>181</v>
+      </c>
+      <c r="D6" s="17">
         <v>3000</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2730,16 +2763,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D7" s="16">
+        <v>188</v>
+      </c>
+      <c r="D7" s="17">
         <v>27000</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2747,16 +2780,16 @@
         <v>2</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D8" s="16">
+        <v>189</v>
+      </c>
+      <c r="D8" s="17">
         <v>21000</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2764,16 +2797,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="17">
+        <v>20000</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>182</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D9" s="16">
-        <v>20000</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2781,16 +2814,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D10" s="16">
+        <v>186</v>
+      </c>
+      <c r="D10" s="17">
         <v>40000</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2798,16 +2831,16 @@
         <v>3</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="16">
+        <v>188</v>
+      </c>
+      <c r="D11" s="17">
         <v>27000</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2815,16 +2848,16 @@
         <v>3</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D12" s="16">
+        <v>189</v>
+      </c>
+      <c r="D12" s="17">
         <v>21000</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2832,16 +2865,16 @@
         <v>4</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="17">
+        <v>20000</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>182</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D13" s="16">
-        <v>20000</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2849,16 +2882,16 @@
         <v>4</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D14" s="16">
+        <v>186</v>
+      </c>
+      <c r="D14" s="17">
         <v>40000</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2866,16 +2899,16 @@
         <v>4</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D15" s="16">
+        <v>189</v>
+      </c>
+      <c r="D15" s="17">
         <v>21000</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2883,16 +2916,16 @@
         <v>5</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="17">
+        <v>20000</v>
+      </c>
+      <c r="E16" s="15" t="s">
         <v>182</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D16" s="16">
-        <v>20000</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2900,16 +2933,16 @@
         <v>5</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D17" s="16">
+        <v>186</v>
+      </c>
+      <c r="D17" s="17">
         <v>40000</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2917,16 +2950,16 @@
         <v>6</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="16">
+        <v>190</v>
+      </c>
+      <c r="D18" s="17">
         <v>50000</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2966,7 +2999,7 @@
         <v>24</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>71</v>
@@ -2977,10 +3010,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2988,10 +3021,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2999,10 +3032,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -3033,79 +3066,79 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="C2" s="17" t="s">
         <v>202</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C3" s="17" t="s">
         <v>205</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="C4" s="17" t="s">
         <v>208</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B5" s="8">
         <v>48</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>210</v>
+      <c r="C5" s="18" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C6" s="17" t="s">
         <v>213</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="C7" s="17" t="s">
         <v>216</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/data/durf-roadmap.xlsx
+++ b/data/durf-roadmap.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="237">
   <si>
     <t xml:space="preserve">DURF roadmap — how to edit this workbook</t>
   </si>
@@ -277,6 +277,9 @@
     <t xml:space="preserve">Not started</t>
   </si>
   <si>
+    <t xml:space="preserve">Needs feedback and approval from all UKBs</t>
+  </si>
+  <si>
     <t xml:space="preserve">Establish NaMeCo (Dutch National Membership Consortium for OpenAIRE representation)</t>
   </si>
   <si>
@@ -289,12 +292,18 @@
     <t xml:space="preserve">NaMeCo template :: https://www.openaire.eu/public-documents/nameco-template</t>
   </si>
   <si>
+    <t xml:space="preserve">Legal adviced needed on type of consortium</t>
+  </si>
+  <si>
     <t xml:space="preserve">Draft and finalize formal agreements on roles and responsibilities between SURF, NaMeCo institutions, KB National Library, publishers, and OpenAIRE</t>
   </si>
   <si>
     <t xml:space="preserve">Draft &amp; Signed Federation Rule Book.</t>
   </si>
   <si>
+    <t xml:space="preserve">Part of same issue as above</t>
+  </si>
+  <si>
     <t xml:space="preserve">Define legal structure for CC0 metadata influx</t>
   </si>
   <si>
@@ -307,12 +316,24 @@
     <t xml:space="preserve">6</t>
   </si>
   <si>
+    <t xml:space="preserve">Execution of this task needs some thinking. WHo else is needed to help</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relate to Barcelona Declaration working group. WHo will do this work in DURF?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, this is a separate legal issue</t>
+  </si>
+  <si>
     <t xml:space="preserve">Create a comprehensive governance framework for all project themes</t>
   </si>
   <si>
     <t xml:space="preserve">Project governance framework.</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes. This  comes first and defines  the legal requirements for deliverables 2 and 3 in this list</t>
+  </si>
+  <si>
     <t xml:space="preserve">Organize annual National Symposium and General Assembly for federation members</t>
   </si>
   <si>
@@ -325,7 +346,7 @@
     <t xml:space="preserve">12, 24, 36, 48</t>
   </si>
   <si>
-    <t xml:space="preserve">Budget: € 23.000 per symposium × 4.</t>
+    <t xml:space="preserve">Budget: € 23.000 per symposium × 4. TO be organised by project management team?</t>
   </si>
   <si>
     <t xml:space="preserve">Review and update governance framework to ensure post-project sustainability</t>
@@ -343,6 +364,12 @@
     <t xml:space="preserve">EduStandaard werkgroepen :: https://www.edustandaard.nl/standaard_werkgroepen/</t>
   </si>
   <si>
+    <t xml:space="preserve">Needs inventory of current contracts (KB, DANS) and approval and feedback from all members (both UKB and non-UKB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help with setting up contract and evaluating existing contracts and agreements (URN:NBN, ISNI, Orcid, Narcis,KB  e-depot). Check theme 4 for duplication.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Develop updated metadata application profile; translating current NL-DIDL-MODS requirements to OpenAIRE CERIF and DC guidelines</t>
   </si>
   <si>
@@ -355,6 +382,12 @@
     <t xml:space="preserve">NL-DIDL-MODS :: https://www.edustandaard.nl/standaard_afspraken/?edu_orderby=title&amp;werkgebieden%5B%5D=ho&amp;registratiestatussen%5B%5D=geregistreerd&amp;registratiestatussen%5B%5D=aangemeld&amp;gebruiksadviezen%5B%5D=verplicht&amp;gebruiksadviezen%5B%5D=aangeraden&amp;gebruiksadviezen%5B%5D=onder-voorwaarden&amp;gebruiksadviezen%5B%5D=onbekend | OpenAIRE CERIF and DC guidelines :: https://guidelines.openaire.eu/ | RSL: Really Simple Licensing :: https://rslstandard.org/</t>
   </si>
   <si>
+    <t xml:space="preserve">Small committee of 6-8 members for reviewing and elaborating upon the standards. Proposed time needed 3-4 half day meetings + homework (48 hours)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information on copyright for metadata, in particular the abstract,privacy versus CERIF person information and once at OpenAIRE the AI enrichment and further dissemination as CC0. For this we also need to evaluate vendor contracts (for example Pure/Converis). </t>
+  </si>
+  <si>
     <t xml:space="preserve">Support repositories, CRIS systems, and KB eDepot in adopting the updated profile</t>
   </si>
   <si>
@@ -364,6 +397,9 @@
     <t xml:space="preserve">configuration</t>
   </si>
   <si>
+    <t xml:space="preserve">Pure-user group for implementing changes in Pure. All repository/CRIS managers to implement standards locally.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitor compliance with the new standard and share implementation best practices</t>
   </si>
   <si>
@@ -376,6 +412,9 @@
     <t xml:space="preserve">CRIS/Repo Dashboard :: https://surf-ori.github.io/dashboards/cris-repository-overview.html</t>
   </si>
   <si>
+    <t xml:space="preserve">Small committee to create an overview of best practices. All for a meeting to share best practices.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Develop proof of concept for enriching local metadata with the OpenAIRE data broker</t>
   </si>
   <si>
@@ -388,6 +427,9 @@
     <t xml:space="preserve">OpenAIRE Broker :: https://catalogue.openaire.eu/service/openaire.broker/overview | Example broker feed :: https://provide.openaire.eu/repository/eurocrisdris::01222/events</t>
   </si>
   <si>
+    <t xml:space="preserve">Two or three institutions willing to implement enrichment. Focus should be on Pure and D-Space as common platforms. Implementing may be time intensive.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitor usage of core entity PIDs (ROR, ORCiD, DOI) and promote local implementation</t>
   </si>
   <si>
@@ -397,6 +439,9 @@
     <t xml:space="preserve">software, service</t>
   </si>
   <si>
+    <t xml:space="preserve">Small committee (3-4 institutions) to create materials for better coverage of identifiers to be shared with partners. Research intelligence teams of all members for promoting implementation in the universities. (data model is part of the application profile)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Launch download statistics sharing pilot on OpenAIRE</t>
   </si>
   <si>
@@ -404,6 +449,9 @@
   </si>
   <si>
     <t xml:space="preserve">OpenAIRE Usage Counts :: https://catalogue.openaire.eu/service/openaire.usagecounts/overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferrably 2-3 institutions willing to trial sharing usage data and wanting to develop a local implementation (available for D-Space, not yet for Pure and other systems)..</t>
   </si>
   <si>
     <t xml:space="preserve">Establish baseline metrics and reporting system for full-text uptake</t>
@@ -417,6 +465,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Write a proposal (2)
 </t>
@@ -466,6 +515,9 @@
     <t xml:space="preserve">training</t>
   </si>
   <si>
+    <t xml:space="preserve">Inventory on of liability issues by adding fulltext (and enriching metadata) automatically as opposed to having a researcher do it. Guidance on further usage of fulltext content for example in a datawarehouse OpenAIRE might create on our behalf.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Implement pull mechanism for metadata and full-text publications, partly via OpenAIRE</t>
   </si>
   <si>
@@ -505,6 +557,9 @@
     <t xml:space="preserve">Google Scholar inclusion guidelines :: https://scholar.google.com/intl/en/scholar/inclusion.html</t>
   </si>
   <si>
+    <t xml:space="preserve">Commission of 6-8 members, preferably the same as for theme 2. Group consensus (questionnaire) to decide what initiatives to focus on.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Implement DOI-minting capabilities for grey literature in DURF repositories</t>
   </si>
   <si>
@@ -512,6 +567,9 @@
   </si>
   <si>
     <t xml:space="preserve">configuration, software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Intelligence (see theme 2) assistance to lobby the functionality being  added locally. Co-operation from the members that do not have DOI minting yet.</t>
   </si>
   <si>
     <t xml:space="preserve">Create monitoring system for tracking DURF content visibility across major indexes</t>
@@ -774,6 +832,7 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -784,7 +843,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -831,6 +890,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF83201B"/>
         <bgColor rgb="FF800000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF4000"/>
+        <bgColor rgb="FFEE7628"/>
       </patternFill>
     </fill>
   </fills>
@@ -883,7 +948,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -948,6 +1013,14 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -991,7 +1064,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFFF4000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1747,7 +1820,9 @@
         <v>80</v>
       </c>
       <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="K2" s="8" t="s">
+        <v>81</v>
+      </c>
       <c r="L2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1755,13 +1830,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E3" s="15">
         <v>1</v>
@@ -1771,27 +1846,29 @@
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="L3" s="8" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15">
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4" s="15">
         <v>1</v>
@@ -1808,47 +1885,55 @@
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="L4" s="8" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15">
         <v>1</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="15">
+        <v>92</v>
+      </c>
+      <c r="E5" s="16">
         <v>6</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="16">
         <v>6</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
+      <c r="J5" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15">
         <v>1</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>78</v>
@@ -1865,7 +1950,9 @@
         <v>80</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
+      <c r="K6" s="8" t="s">
+        <v>99</v>
+      </c>
       <c r="L6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1873,13 +1960,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E7" s="15">
         <v>12</v>
@@ -1888,14 +1975,14 @@
         <v>48</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
@@ -1905,10 +1992,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>78</v>
@@ -1933,13 +2020,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E9" s="15">
         <v>1</v>
@@ -1949,27 +2036,31 @@
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="8" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
+      <c r="K9" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15">
         <v>2</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E10" s="15">
         <v>3</v>
@@ -1979,27 +2070,31 @@
       </c>
       <c r="G10" s="15"/>
       <c r="H10" s="8" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
+      <c r="K10" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15">
         <v>2</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E11" s="15">
         <v>12</v>
@@ -2013,7 +2108,9 @@
         <v>80</v>
       </c>
       <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
+      <c r="K11" s="8" t="s">
+        <v>121</v>
+      </c>
       <c r="L11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2021,13 +2118,13 @@
         <v>2</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E12" s="15">
         <v>12</v>
@@ -2037,13 +2134,15 @@
       </c>
       <c r="G12" s="15"/>
       <c r="H12" s="8" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
+      <c r="K12" s="8" t="s">
+        <v>126</v>
+      </c>
       <c r="L12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2051,13 +2150,13 @@
         <v>2</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E13" s="15">
         <v>12</v>
@@ -2067,13 +2166,15 @@
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="8" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
+      <c r="K13" s="8" t="s">
+        <v>131</v>
+      </c>
       <c r="L13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2081,13 +2182,13 @@
         <v>2</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E14" s="15">
         <v>12</v>
@@ -2097,13 +2198,15 @@
       </c>
       <c r="G14" s="15"/>
       <c r="H14" s="8" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
+      <c r="K14" s="8" t="s">
+        <v>135</v>
+      </c>
       <c r="L14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2111,13 +2214,13 @@
         <v>2</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E15" s="15">
         <v>12</v>
@@ -2127,13 +2230,15 @@
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="8" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
+      <c r="K15" s="17" t="s">
+        <v>139</v>
+      </c>
       <c r="L15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2141,13 +2246,13 @@
         <v>3</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E16" s="15">
         <v>1</v>
@@ -2155,18 +2260,18 @@
       <c r="F16" s="15">
         <v>6</v>
       </c>
-      <c r="G16" s="16" t="s">
-        <v>126</v>
+      <c r="G16" s="18" t="s">
+        <v>142</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="L16" s="8"/>
     </row>
@@ -2175,10 +2280,10 @@
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>78</v>
@@ -2203,13 +2308,13 @@
         <v>3</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="E18" s="15">
         <v>12</v>
@@ -2231,13 +2336,13 @@
         <v>3</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="E19" s="15">
         <v>24</v>
@@ -2252,20 +2357,22 @@
       </c>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
+      <c r="L19" s="8" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15">
         <v>4</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="E20" s="15">
         <v>3</v>
@@ -2287,13 +2394,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="E21" s="15">
         <v>12</v>
@@ -2315,13 +2422,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E22" s="15">
         <v>12</v>
@@ -2331,7 +2438,7 @@
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="8" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>80</v>
@@ -2345,13 +2452,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="E23" s="15">
         <v>12</v>
@@ -2373,10 +2480,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>78</v>
@@ -2389,13 +2496,15 @@
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="8" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
+      <c r="K24" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="L24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2403,13 +2512,13 @@
         <v>5</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="E25" s="15">
         <v>6</v>
@@ -2423,7 +2532,9 @@
         <v>80</v>
       </c>
       <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
+      <c r="K25" s="8" t="s">
+        <v>171</v>
+      </c>
       <c r="L25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2431,13 +2542,13 @@
         <v>5</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E26" s="15">
         <v>12</v>
@@ -2447,7 +2558,7 @@
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="8" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>80</v>
@@ -2461,13 +2572,13 @@
         <v>6</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E27" s="15">
         <v>1</v>
@@ -2476,14 +2587,14 @@
         <v>25</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
@@ -2493,10 +2604,10 @@
         <v>6</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>78</v>
@@ -2508,14 +2619,14 @@
         <v>42</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
@@ -2525,10 +2636,10 @@
         <v>6</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>78</v>
@@ -2540,14 +2651,14 @@
         <v>45</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
@@ -2557,13 +2668,13 @@
         <v>6</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E30" s="15">
         <v>12</v>
@@ -2572,14 +2683,14 @@
         <v>48</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H30" s="8"/>
       <c r="I30" s="7" t="s">
         <v>80</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
@@ -2589,13 +2700,13 @@
         <v>6</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E31" s="15">
         <v>9</v>
@@ -2604,7 +2715,7 @@
         <v>9</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="H31" s="8"/>
       <c r="I31" s="7" t="s">
@@ -2661,16 +2772,16 @@
         <v>24</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2678,16 +2789,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="D2" s="17">
+        <v>197</v>
+      </c>
+      <c r="D2" s="19">
         <v>92000</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2695,16 +2806,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3" s="17">
+        <v>200</v>
+      </c>
+      <c r="D3" s="19">
         <v>3000</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2712,16 +2823,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" s="17">
+        <v>203</v>
+      </c>
+      <c r="D4" s="19">
         <v>20000</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2729,16 +2840,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D5" s="17">
+        <v>205</v>
+      </c>
+      <c r="D5" s="19">
         <v>40000</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2746,16 +2857,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="D6" s="17">
+        <v>200</v>
+      </c>
+      <c r="D6" s="19">
         <v>3000</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2763,16 +2874,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D7" s="17">
+        <v>207</v>
+      </c>
+      <c r="D7" s="19">
         <v>27000</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2780,16 +2891,16 @@
         <v>2</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D8" s="17">
+        <v>208</v>
+      </c>
+      <c r="D8" s="19">
         <v>21000</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2797,16 +2908,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="17">
+        <v>203</v>
+      </c>
+      <c r="D9" s="19">
         <v>20000</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2814,16 +2925,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D10" s="17">
+        <v>205</v>
+      </c>
+      <c r="D10" s="19">
         <v>40000</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2831,16 +2942,16 @@
         <v>3</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="17">
+        <v>207</v>
+      </c>
+      <c r="D11" s="19">
         <v>27000</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2848,16 +2959,16 @@
         <v>3</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D12" s="17">
+        <v>208</v>
+      </c>
+      <c r="D12" s="19">
         <v>21000</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2865,16 +2976,16 @@
         <v>4</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D13" s="17">
+        <v>203</v>
+      </c>
+      <c r="D13" s="19">
         <v>20000</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2882,16 +2993,16 @@
         <v>4</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D14" s="17">
+        <v>205</v>
+      </c>
+      <c r="D14" s="19">
         <v>40000</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2899,16 +3010,16 @@
         <v>4</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D15" s="17">
+        <v>208</v>
+      </c>
+      <c r="D15" s="19">
         <v>21000</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2916,16 +3027,16 @@
         <v>5</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D16" s="17">
+        <v>203</v>
+      </c>
+      <c r="D16" s="19">
         <v>20000</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2933,16 +3044,16 @@
         <v>5</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D17" s="17">
+        <v>205</v>
+      </c>
+      <c r="D17" s="19">
         <v>40000</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2950,16 +3061,16 @@
         <v>6</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="D18" s="17">
+        <v>209</v>
+      </c>
+      <c r="D18" s="19">
         <v>50000</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2999,7 +3110,7 @@
         <v>24</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>71</v>
@@ -3010,10 +3121,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3021,10 +3132,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3032,10 +3143,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -3066,79 +3177,79 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>203</v>
+        <v>221</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>206</v>
+        <v>224</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>209</v>
+        <v>227</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="B5" s="8">
         <v>48</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>211</v>
+      <c r="C5" s="20" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>214</v>
+        <v>232</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>217</v>
+        <v>235</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
